--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N10_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>79.78226463386203</v>
       </c>
       <c r="E2" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F2" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>62.8602835369126</v>
       </c>
       <c r="E3" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F3" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>59.45511117734795</v>
       </c>
       <c r="E4" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F4" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>19.93510181294701</v>
       </c>
       <c r="E5" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F5" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>7.674549187147864</v>
       </c>
       <c r="E6" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F6" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>17.97825969484754</v>
       </c>
       <c r="E7" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F7" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>54.9783432448288</v>
       </c>
       <c r="E8" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F8" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>15.47624140790756</v>
       </c>
       <c r="E9" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F9" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>67.09133695799531</v>
       </c>
       <c r="E10" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F10" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>61.19631327472839</v>
       </c>
       <c r="E11" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F11" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>50.86825906053703</v>
       </c>
       <c r="E12" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F12" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         <v>70.22728164842664</v>
       </c>
       <c r="E13" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F13" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>87.48955031576767</v>
       </c>
       <c r="E14" t="n">
-        <v>26.02043637872185</v>
+        <v>26.49046133508399</v>
       </c>
       <c r="F14" t="n">
-        <v>25.98314437661264</v>
+        <v>26.44558617045711</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,23 +896,55 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
+        <v>14.51368083337119</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14.51935367299663</v>
+      </c>
+      <c r="E15" t="n">
+        <v>26.49046133508399</v>
+      </c>
+      <c r="F15" t="n">
+        <v>26.44558617045711</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>T6758</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>W0045F0001T0006Z000C1N10.png</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
         <v>15.56609819838121</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>15.32174523288773</v>
       </c>
-      <c r="E15" t="n">
-        <v>26.02043637872185</v>
-      </c>
-      <c r="F15" t="n">
-        <v>25.98314437661264</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>T6758</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="E16" t="n">
+        <v>26.49046133508399</v>
+      </c>
+      <c r="F16" t="n">
+        <v>26.44558617045711</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>T6758</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.68727957140628</v>
+        <v>12.94918293035352</v>
       </c>
       <c r="D2" t="n">
-        <v>79.78226463386203</v>
+        <v>12.96461800300258</v>
       </c>
       <c r="E2" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F2" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.8025212303639</v>
+        <v>10.20540969993414</v>
       </c>
       <c r="D3" t="n">
-        <v>62.8602835369126</v>
+        <v>10.2147960747483</v>
       </c>
       <c r="E3" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F3" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.94860220609218</v>
+        <v>9.90414785848998</v>
       </c>
       <c r="D4" t="n">
-        <v>59.45511117734795</v>
+        <v>9.661455566319043</v>
       </c>
       <c r="E4" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F4" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.84406426542864</v>
+        <v>3.224660443132155</v>
       </c>
       <c r="D5" t="n">
-        <v>19.93510181294701</v>
+        <v>3.239454044603889</v>
       </c>
       <c r="E5" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F5" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.646609841085894</v>
+        <v>1.242574099176458</v>
       </c>
       <c r="D6" t="n">
-        <v>7.674549187147864</v>
+        <v>1.247114242911528</v>
       </c>
       <c r="E6" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F6" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.97244184829017</v>
+        <v>2.920521800347152</v>
       </c>
       <c r="D7" t="n">
-        <v>17.97825969484754</v>
+        <v>2.921467200412725</v>
       </c>
       <c r="E7" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F7" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.99005246898705</v>
+        <v>8.935883526210395</v>
       </c>
       <c r="D8" t="n">
-        <v>54.9783432448288</v>
+        <v>8.933980777284681</v>
       </c>
       <c r="E8" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F8" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.54635298074958</v>
+        <v>2.526282359371806</v>
       </c>
       <c r="D9" t="n">
-        <v>15.47624140790756</v>
+        <v>2.514889228784978</v>
       </c>
       <c r="E9" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F9" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>67.11010943589083</v>
+        <v>10.90539278333226</v>
       </c>
       <c r="D10" t="n">
-        <v>67.09133695799531</v>
+        <v>10.90234225567424</v>
       </c>
       <c r="E10" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F10" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.22254159675316</v>
+        <v>9.948663009472389</v>
       </c>
       <c r="D11" t="n">
-        <v>61.19631327472839</v>
+        <v>9.944400907143363</v>
       </c>
       <c r="E11" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F11" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>50.96687292073208</v>
+        <v>8.282116849618964</v>
       </c>
       <c r="D12" t="n">
-        <v>50.86825906053703</v>
+        <v>8.266092097337268</v>
       </c>
       <c r="E12" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F12" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>70.28672888572069</v>
+        <v>11.42159344392961</v>
       </c>
       <c r="D13" t="n">
-        <v>70.22728164842664</v>
+        <v>11.41193326786933</v>
       </c>
       <c r="E13" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F13" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>87.56795550585447</v>
+        <v>14.22979276970135</v>
       </c>
       <c r="D14" t="n">
-        <v>87.48955031576767</v>
+        <v>14.21705192631225</v>
       </c>
       <c r="E14" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F14" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>14.51368083337119</v>
+        <v>2.358473135422819</v>
       </c>
       <c r="D15" t="n">
-        <v>14.51935367299663</v>
+        <v>2.359394971861953</v>
       </c>
       <c r="E15" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F15" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.56609819838121</v>
+        <v>2.529490957236947</v>
       </c>
       <c r="D16" t="n">
-        <v>15.32174523288773</v>
+        <v>2.489783600344257</v>
       </c>
       <c r="E16" t="n">
-        <v>26.49046133508399</v>
+        <v>4.304699966951147</v>
       </c>
       <c r="F16" t="n">
-        <v>26.44558617045711</v>
+        <v>4.29740775269928</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
